--- a/review-results/河北实时运行及市场出清数据-20260909.xlsx
+++ b/review-results/河北实时运行及市场出清数据-20260909.xlsx
@@ -4284,7 +4284,9 @@
       <s:c r="C2" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D2" s="1"/>
+      <s:c r="D2" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E2" s="1" t="n">
         <s:v>385.73</s:v>
       </s:c>
@@ -4332,7 +4334,9 @@
       <s:c r="C3" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D3" s="1"/>
+      <s:c r="D3" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E3" s="1" t="n">
         <s:v>398.23</s:v>
       </s:c>
@@ -4380,7 +4384,9 @@
       <s:c r="C4" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D4" s="1"/>
+      <s:c r="D4" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E4" s="1" t="n">
         <s:v>391.42</s:v>
       </s:c>
@@ -4428,7 +4434,9 @@
       <s:c r="C5" s="1" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D5" s="1"/>
+      <s:c r="D5" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E5" s="1" t="n">
         <s:v>398.57</s:v>
       </s:c>
@@ -4476,7 +4484,9 @@
       <s:c r="C6" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D6" s="1"/>
+      <s:c r="D6" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E6" s="1" t="n">
         <s:v>399.32</s:v>
       </s:c>
@@ -4524,7 +4534,9 @@
       <s:c r="C7" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D7" s="1"/>
+      <s:c r="D7" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E7" s="1" t="n">
         <s:v>399.73</s:v>
       </s:c>
@@ -4572,7 +4584,9 @@
       <s:c r="C8" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D8" s="1"/>
+      <s:c r="D8" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E8" s="1" t="n">
         <s:v>390.88</s:v>
       </s:c>
@@ -4620,7 +4634,9 @@
       <s:c r="C9" s="1" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="D9" s="1"/>
+      <s:c r="D9" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E9" s="1" t="n">
         <s:v>390.25</s:v>
       </s:c>
@@ -4668,7 +4684,9 @@
       <s:c r="C10" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D10" s="1"/>
+      <s:c r="D10" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E10" s="1" t="n">
         <s:v>399.45</s:v>
       </s:c>
@@ -4716,7 +4734,9 @@
       <s:c r="C11" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D11" s="1"/>
+      <s:c r="D11" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E11" s="1" t="n">
         <s:v>391.73</s:v>
       </s:c>
@@ -4764,7 +4784,9 @@
       <s:c r="C12" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D12" s="1"/>
+      <s:c r="D12" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E12" s="1" t="n">
         <s:v>400.51</s:v>
       </s:c>
@@ -4812,7 +4834,9 @@
       <s:c r="C13" s="1" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D13" s="1"/>
+      <s:c r="D13" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E13" s="1" t="n">
         <s:v>389.89</s:v>
       </s:c>
@@ -4860,7 +4884,9 @@
       <s:c r="C14" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="1"/>
+      <s:c r="D14" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E14" s="1" t="n">
         <s:v>391.17</s:v>
       </s:c>
@@ -4908,7 +4934,9 @@
       <s:c r="C15" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="1"/>
+      <s:c r="D15" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E15" s="1" t="n">
         <s:v>382.47</s:v>
       </s:c>
@@ -4956,7 +4984,9 @@
       <s:c r="C16" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="1"/>
+      <s:c r="D16" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E16" s="1" t="n">
         <s:v>391.26</s:v>
       </s:c>
@@ -5004,7 +5034,9 @@
       <s:c r="C17" s="1" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="1"/>
+      <s:c r="D17" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E17" s="1" t="n">
         <s:v>389.79</s:v>
       </s:c>
@@ -5052,7 +5084,9 @@
       <s:c r="C18" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D18" s="1"/>
+      <s:c r="D18" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E18" s="1" t="n">
         <s:v>382.23</s:v>
       </s:c>
@@ -5100,7 +5134,9 @@
       <s:c r="C19" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D19" s="1"/>
+      <s:c r="D19" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E19" s="1" t="n">
         <s:v>383.04</s:v>
       </s:c>
@@ -5148,7 +5184,9 @@
       <s:c r="C20" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D20" s="1"/>
+      <s:c r="D20" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E20" s="1" t="n">
         <s:v>389.35</s:v>
       </s:c>
@@ -5196,7 +5234,9 @@
       <s:c r="C21" s="1" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="D21" s="1"/>
+      <s:c r="D21" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E21" s="1" t="n">
         <s:v>390.25</s:v>
       </s:c>
@@ -5244,7 +5284,9 @@
       <s:c r="C22" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D22" s="1"/>
+      <s:c r="D22" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E22" s="1" t="n">
         <s:v>392.1</s:v>
       </s:c>
@@ -5292,7 +5334,9 @@
       <s:c r="C23" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D23" s="1"/>
+      <s:c r="D23" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E23" s="1" t="n">
         <s:v>400.51</s:v>
       </s:c>
@@ -5340,7 +5384,9 @@
       <s:c r="C24" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D24" s="1"/>
+      <s:c r="D24" s="1" t="n">
+        <s:v>416.2</s:v>
+      </s:c>
       <s:c r="E24" s="1" t="n">
         <s:v>399.29</s:v>
       </s:c>
@@ -5388,7 +5434,9 @@
       <s:c r="C25" s="1" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D25" s="1"/>
+      <s:c r="D25" s="1" t="n">
+        <s:v>389.23</s:v>
+      </s:c>
       <s:c r="E25" s="1" t="n">
         <s:v>403.23</s:v>
       </s:c>
@@ -5436,7 +5484,9 @@
       <s:c r="C26" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D26" s="1"/>
+      <s:c r="D26" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E26" s="1" t="n">
         <s:v>407.67</s:v>
       </s:c>
@@ -5484,7 +5534,9 @@
       <s:c r="C27" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D27" s="1"/>
+      <s:c r="D27" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E27" s="1" t="n">
         <s:v>403.23</s:v>
       </s:c>
@@ -5532,7 +5584,9 @@
       <s:c r="C28" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D28" s="1"/>
+      <s:c r="D28" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E28" s="1" t="n">
         <s:v>409.51</s:v>
       </s:c>
@@ -5580,7 +5634,9 @@
       <s:c r="C29" s="1" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="D29" s="1"/>
+      <s:c r="D29" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E29" s="1" t="n">
         <s:v>416.04</s:v>
       </s:c>
@@ -5628,7 +5684,9 @@
       <s:c r="C30" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D30" s="1"/>
+      <s:c r="D30" s="1" t="n">
+        <s:v>389.23</s:v>
+      </s:c>
       <s:c r="E30" s="1" t="n">
         <s:v>416.04</s:v>
       </s:c>
@@ -5676,7 +5734,9 @@
       <s:c r="C31" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D31" s="1"/>
+      <s:c r="D31" s="1" t="n">
+        <s:v>389.23</s:v>
+      </s:c>
       <s:c r="E31" s="1" t="n">
         <s:v>404.01</s:v>
       </s:c>
@@ -5724,7 +5784,9 @@
       <s:c r="C32" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D32" s="1"/>
+      <s:c r="D32" s="1" t="n">
+        <s:v>389.23</s:v>
+      </s:c>
       <s:c r="E32" s="1" t="n">
         <s:v>381.64</s:v>
       </s:c>
@@ -5772,7 +5834,9 @@
       <s:c r="C33" s="1" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="D33" s="1"/>
+      <s:c r="D33" s="1" t="n">
+        <s:v>389.23</s:v>
+      </s:c>
       <s:c r="E33" s="1" t="n">
         <s:v>382.35</s:v>
       </s:c>
@@ -5820,7 +5884,9 @@
       <s:c r="C34" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D34" s="1"/>
+      <s:c r="D34" s="1" t="n">
+        <s:v>313.76</s:v>
+      </s:c>
       <s:c r="E34" s="1" t="n">
         <s:v>380.63</s:v>
       </s:c>
@@ -5868,7 +5934,9 @@
       <s:c r="C35" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D35" s="1"/>
+      <s:c r="D35" s="1" t="n">
+        <s:v>313.76</s:v>
+      </s:c>
       <s:c r="E35" s="1" t="n">
         <s:v>383.17</s:v>
       </s:c>
@@ -5916,7 +5984,9 @@
       <s:c r="C36" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D36" s="1"/>
+      <s:c r="D36" s="1" t="n">
+        <s:v>313.76</s:v>
+      </s:c>
       <s:c r="E36" s="1" t="n">
         <s:v>380.73</s:v>
       </s:c>
@@ -5964,7 +6034,9 @@
       <s:c r="C37" s="1" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="D37" s="1"/>
+      <s:c r="D37" s="1" t="n">
+        <s:v>313.76</s:v>
+      </s:c>
       <s:c r="E37" s="1" t="n">
         <s:v>368.42</s:v>
       </s:c>
@@ -6012,7 +6084,9 @@
       <s:c r="C38" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D38" s="1"/>
+      <s:c r="D38" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E38" s="1" t="n">
         <s:v>372.61</s:v>
       </s:c>
@@ -6060,7 +6134,9 @@
       <s:c r="C39" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D39" s="1"/>
+      <s:c r="D39" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E39" s="1" t="n">
         <s:v>369.17</s:v>
       </s:c>
@@ -6108,7 +6184,9 @@
       <s:c r="C40" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D40" s="1"/>
+      <s:c r="D40" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E40" s="1" t="n">
         <s:v>363.7</s:v>
       </s:c>
@@ -6156,7 +6234,9 @@
       <s:c r="C41" s="1" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D41" s="1"/>
+      <s:c r="D41" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E41" s="1" t="n">
         <s:v>364.41</s:v>
       </s:c>
@@ -6204,7 +6284,9 @@
       <s:c r="C42" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D42" s="1"/>
+      <s:c r="D42" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E42" s="1" t="n">
         <s:v>363.83</s:v>
       </s:c>
@@ -6252,7 +6334,9 @@
       <s:c r="C43" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D43" s="1"/>
+      <s:c r="D43" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E43" s="1" t="n">
         <s:v>363.3</s:v>
       </s:c>
@@ -6300,7 +6384,9 @@
       <s:c r="C44" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D44" s="1"/>
+      <s:c r="D44" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E44" s="1" t="n">
         <s:v>364.41</s:v>
       </s:c>
@@ -6348,7 +6434,9 @@
       <s:c r="C45" s="1" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="D45" s="1"/>
+      <s:c r="D45" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E45" s="1" t="n">
         <s:v>360.16</s:v>
       </s:c>
@@ -6396,7 +6484,9 @@
       <s:c r="C46" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D46" s="1"/>
+      <s:c r="D46" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E46" s="1" t="n">
         <s:v>354.32</s:v>
       </s:c>
@@ -6444,7 +6534,9 @@
       <s:c r="C47" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D47" s="1"/>
+      <s:c r="D47" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E47" s="1" t="n">
         <s:v>431.29</s:v>
       </s:c>
@@ -6492,7 +6584,9 @@
       <s:c r="C48" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D48" s="1"/>
+      <s:c r="D48" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E48" s="1" t="n">
         <s:v>378.51</s:v>
       </s:c>
@@ -6540,7 +6634,9 @@
       <s:c r="C49" s="1" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="D49" s="1"/>
+      <s:c r="D49" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E49" s="1" t="n">
         <s:v>382.92</s:v>
       </s:c>
@@ -6588,7 +6684,9 @@
       <s:c r="C50" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D50" s="1"/>
+      <s:c r="D50" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E50" s="1" t="n">
         <s:v>353.01</s:v>
       </s:c>
@@ -6636,7 +6734,9 @@
       <s:c r="C51" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D51" s="1"/>
+      <s:c r="D51" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E51" s="1" t="n">
         <s:v>274.33</s:v>
       </s:c>
@@ -6684,7 +6784,9 @@
       <s:c r="C52" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D52" s="1"/>
+      <s:c r="D52" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E52" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6732,7 +6834,9 @@
       <s:c r="C53" s="1" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="D53" s="1"/>
+      <s:c r="D53" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E53" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6780,7 +6884,9 @@
       <s:c r="C54" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D54" s="1"/>
+      <s:c r="D54" s="1" t="n">
+        <s:v>274.33</s:v>
+      </s:c>
       <s:c r="E54" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6828,7 +6934,9 @@
       <s:c r="C55" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D55" s="1"/>
+      <s:c r="D55" s="1" t="n">
+        <s:v>274.33</s:v>
+      </s:c>
       <s:c r="E55" s="1" t="n">
         <s:v>0</s:v>
       </s:c>
@@ -6876,7 +6984,9 @@
       <s:c r="C56" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D56" s="1"/>
+      <s:c r="D56" s="1" t="n">
+        <s:v>274.33</s:v>
+      </s:c>
       <s:c r="E56" s="1" t="n">
         <s:v>274.33</s:v>
       </s:c>
@@ -6924,7 +7034,9 @@
       <s:c r="C57" s="1" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="D57" s="1"/>
+      <s:c r="D57" s="1" t="n">
+        <s:v>274.33</s:v>
+      </s:c>
       <s:c r="E57" s="1" t="n">
         <s:v>352.22</s:v>
       </s:c>
@@ -6972,7 +7084,9 @@
       <s:c r="C58" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D58" s="1"/>
+      <s:c r="D58" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E58" s="1" t="n">
         <s:v>355.3</s:v>
       </s:c>
@@ -7020,7 +7134,9 @@
       <s:c r="C59" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D59" s="1"/>
+      <s:c r="D59" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E59" s="1" t="n">
         <s:v>355.7</s:v>
       </s:c>
@@ -7068,7 +7184,9 @@
       <s:c r="C60" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D60" s="1"/>
+      <s:c r="D60" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E60" s="1" t="n">
         <s:v>366.16</s:v>
       </s:c>
@@ -7116,7 +7234,9 @@
       <s:c r="C61" s="1" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="D61" s="1"/>
+      <s:c r="D61" s="1" t="n">
+        <s:v>275.79</s:v>
+      </s:c>
       <s:c r="E61" s="1" t="n">
         <s:v>356.01</s:v>
       </s:c>
@@ -7164,7 +7284,9 @@
       <s:c r="C62" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D62" s="1"/>
+      <s:c r="D62" s="1" t="n">
+        <s:v>352.7</s:v>
+      </s:c>
       <s:c r="E62" s="1" t="n">
         <s:v>355.98</s:v>
       </s:c>
@@ -7212,7 +7334,9 @@
       <s:c r="C63" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D63" s="1"/>
+      <s:c r="D63" s="1" t="n">
+        <s:v>352.7</s:v>
+      </s:c>
       <s:c r="E63" s="1" t="n">
         <s:v>399.1</s:v>
       </s:c>
@@ -7260,7 +7384,9 @@
       <s:c r="C64" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D64" s="1"/>
+      <s:c r="D64" s="1" t="n">
+        <s:v>352.7</s:v>
+      </s:c>
       <s:c r="E64" s="1" t="n">
         <s:v>381.55</s:v>
       </s:c>
@@ -7308,7 +7434,9 @@
       <s:c r="C65" s="1" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="D65" s="1"/>
+      <s:c r="D65" s="1" t="n">
+        <s:v>314.77</s:v>
+      </s:c>
       <s:c r="E65" s="1" t="n">
         <s:v>400.6</s:v>
       </s:c>
@@ -7356,7 +7484,9 @@
       <s:c r="C66" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D66" s="1"/>
+      <s:c r="D66" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E66" s="1" t="n">
         <s:v>394.97</s:v>
       </s:c>
@@ -7404,7 +7534,9 @@
       <s:c r="C67" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D67" s="1"/>
+      <s:c r="D67" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E67" s="1" t="n">
         <s:v>408.69</s:v>
       </s:c>
@@ -7452,7 +7584,9 @@
       <s:c r="C68" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D68" s="1"/>
+      <s:c r="D68" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E68" s="1" t="n">
         <s:v>415.92</s:v>
       </s:c>
@@ -7500,7 +7634,9 @@
       <s:c r="C69" s="1" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="D69" s="1"/>
+      <s:c r="D69" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E69" s="1" t="n">
         <s:v>409.73</s:v>
       </s:c>
@@ -7548,7 +7684,9 @@
       <s:c r="C70" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D70" s="1"/>
+      <s:c r="D70" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E70" s="1" t="n">
         <s:v>416.2</s:v>
       </s:c>
@@ -7596,7 +7734,9 @@
       <s:c r="C71" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D71" s="1"/>
+      <s:c r="D71" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E71" s="1" t="n">
         <s:v>415.92</s:v>
       </s:c>
@@ -7644,7 +7784,9 @@
       <s:c r="C72" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D72" s="1"/>
+      <s:c r="D72" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E72" s="1" t="n">
         <s:v>415.92</s:v>
       </s:c>
@@ -7692,7 +7834,9 @@
       <s:c r="C73" s="1" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="D73" s="1"/>
+      <s:c r="D73" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E73" s="1" t="n">
         <s:v>408.73</s:v>
       </s:c>
@@ -7740,7 +7884,9 @@
       <s:c r="C74" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D74" s="1"/>
+      <s:c r="D74" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E74" s="1" t="n">
         <s:v>407.14</s:v>
       </s:c>
@@ -7788,7 +7934,9 @@
       <s:c r="C75" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D75" s="1"/>
+      <s:c r="D75" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E75" s="1" t="n">
         <s:v>408</s:v>
       </s:c>
@@ -7836,7 +7984,9 @@
       <s:c r="C76" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D76" s="1"/>
+      <s:c r="D76" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E76" s="1" t="n">
         <s:v>408.79</s:v>
       </s:c>
@@ -7884,7 +8034,9 @@
       <s:c r="C77" s="1" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="D77" s="1"/>
+      <s:c r="D77" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E77" s="1" t="n">
         <s:v>407.14</s:v>
       </s:c>
@@ -7932,7 +8084,9 @@
       <s:c r="C78" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D78" s="1"/>
+      <s:c r="D78" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E78" s="1" t="n">
         <s:v>400.7</s:v>
       </s:c>
@@ -7980,7 +8134,9 @@
       <s:c r="C79" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D79" s="1"/>
+      <s:c r="D79" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E79" s="1" t="n">
         <s:v>393.26</s:v>
       </s:c>
@@ -8028,7 +8184,9 @@
       <s:c r="C80" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D80" s="1"/>
+      <s:c r="D80" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E80" s="1" t="n">
         <s:v>391.26</s:v>
       </s:c>
@@ -8076,7 +8234,9 @@
       <s:c r="C81" s="1" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="D81" s="1"/>
+      <s:c r="D81" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E81" s="1" t="n">
         <s:v>391.23</s:v>
       </s:c>
@@ -8124,7 +8284,9 @@
       <s:c r="C82" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D82" s="1"/>
+      <s:c r="D82" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E82" s="1" t="n">
         <s:v>398.57</s:v>
       </s:c>
@@ -8172,7 +8334,9 @@
       <s:c r="C83" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D83" s="1"/>
+      <s:c r="D83" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E83" s="1" t="n">
         <s:v>400.55</s:v>
       </s:c>
@@ -8220,7 +8384,9 @@
       <s:c r="C84" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D84" s="1"/>
+      <s:c r="D84" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E84" s="1" t="n">
         <s:v>400.64</s:v>
       </s:c>
@@ -8268,7 +8434,9 @@
       <s:c r="C85" s="1" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="D85" s="1"/>
+      <s:c r="D85" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E85" s="1" t="n">
         <s:v>399.13</s:v>
       </s:c>
@@ -8316,7 +8484,9 @@
       <s:c r="C86" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D86" s="1"/>
+      <s:c r="D86" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E86" s="1" t="n">
         <s:v>397.98</s:v>
       </s:c>
@@ -8364,7 +8534,9 @@
       <s:c r="C87" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D87" s="1"/>
+      <s:c r="D87" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E87" s="1" t="n">
         <s:v>394.97</s:v>
       </s:c>
@@ -8412,7 +8584,9 @@
       <s:c r="C88" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D88" s="1"/>
+      <s:c r="D88" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E88" s="1" t="n">
         <s:v>390.76</s:v>
       </s:c>
@@ -8460,7 +8634,9 @@
       <s:c r="C89" s="1" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="D89" s="1"/>
+      <s:c r="D89" s="1" t="n">
+        <s:v>381.13</s:v>
+      </s:c>
       <s:c r="E89" s="1" t="n">
         <s:v>392.1</s:v>
       </s:c>
@@ -8508,7 +8684,9 @@
       <s:c r="C90" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D90" s="1"/>
+      <s:c r="D90" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E90" s="1" t="n">
         <s:v>395.35</s:v>
       </s:c>
@@ -8556,7 +8734,9 @@
       <s:c r="C91" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D91" s="1"/>
+      <s:c r="D91" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E91" s="1" t="n">
         <s:v>400.57</s:v>
       </s:c>
@@ -8604,7 +8784,9 @@
       <s:c r="C92" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D92" s="1"/>
+      <s:c r="D92" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E92" s="1" t="n">
         <s:v>400.85</s:v>
       </s:c>
@@ -8652,7 +8834,9 @@
       <s:c r="C93" s="1" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="D93" s="1"/>
+      <s:c r="D93" s="1" t="n">
+        <s:v>425.07</s:v>
+      </s:c>
       <s:c r="E93" s="1" t="n">
         <s:v>407.17</s:v>
       </s:c>
@@ -8700,7 +8884,9 @@
       <s:c r="C94" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D94" s="1"/>
+      <s:c r="D94" s="1" t="n">
+        <s:v>400.92</s:v>
+      </s:c>
       <s:c r="E94" s="1" t="n">
         <s:v>409.76</s:v>
       </s:c>
@@ -8748,7 +8934,9 @@
       <s:c r="C95" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D95" s="1"/>
+      <s:c r="D95" s="1" t="n">
+        <s:v>400.92</s:v>
+      </s:c>
       <s:c r="E95" s="1" t="n">
         <s:v>409.51</s:v>
       </s:c>
@@ -8796,7 +8984,9 @@
       <s:c r="C96" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D96" s="1"/>
+      <s:c r="D96" s="1" t="n">
+        <s:v>400.92</s:v>
+      </s:c>
       <s:c r="E96" s="1" t="n">
         <s:v>407.67</s:v>
       </s:c>
@@ -8846,7 +9036,9 @@
       <s:c r="C97" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="D97" s="1"/>
+      <s:c r="D97" s="1" t="n">
+        <s:v>400.92</s:v>
+      </s:c>
       <s:c r="E97" s="1" t="n">
         <s:v>408.73</s:v>
       </s:c>
